--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.86115566245387</v>
+        <v>4.202437795148755</v>
       </c>
       <c r="D2" t="n">
-        <v>26.11370726368856</v>
+        <v>4.243477430349391</v>
       </c>
       <c r="E2" t="n">
-        <v>5.184000923972269</v>
+        <v>0.8424001501454937</v>
       </c>
       <c r="F2" t="n">
-        <v>8.699332772667278</v>
+        <v>1.413641575558433</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.54193170723126</v>
+        <v>2.363063902425079</v>
       </c>
       <c r="D3" t="n">
-        <v>14.53241353264833</v>
+        <v>2.361517199055353</v>
       </c>
       <c r="E3" t="n">
-        <v>5.184000923972269</v>
+        <v>0.8424001501454937</v>
       </c>
       <c r="F3" t="n">
-        <v>8.699332772667278</v>
+        <v>1.413641575558433</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.74096695407032</v>
+        <v>2.557907130036427</v>
       </c>
       <c r="D4" t="n">
-        <v>16.04390773101677</v>
+        <v>2.607135006290225</v>
       </c>
       <c r="E4" t="n">
-        <v>5.184000923972269</v>
+        <v>0.8424001501454937</v>
       </c>
       <c r="F4" t="n">
-        <v>8.699332772667278</v>
+        <v>1.413641575558433</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.0569819746715</v>
+        <v>4.071759570884119</v>
       </c>
       <c r="D5" t="n">
-        <v>1.636203072307091</v>
+        <v>0.2658829992499022</v>
       </c>
       <c r="E5" t="n">
-        <v>5.184000923972269</v>
+        <v>0.8424001501454937</v>
       </c>
       <c r="F5" t="n">
-        <v>8.699332772667278</v>
+        <v>1.413641575558433</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
